--- a/data/trans_orig/P1409-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1409-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2012</t>
+          <t>Población con diagnóstico de asma en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>22011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26402</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20471</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41646</t>
+          <t>40689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>681280</t>
+          <t>681458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>696438</t>
+          <t>695809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>670648</t>
+          <t>671077</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>687006</t>
+          <t>687497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1358873</t>
+          <t>1359830</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1380048</t>
+          <t>1380914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>27775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42564</t>
+          <t>42625</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62449</t>
+          <t>62233</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>991198</t>
+          <t>990172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1007687</t>
+          <t>1007731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>985227</t>
+          <t>985166</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1008947</t>
+          <t>1008382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1983289</t>
+          <t>1983505</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2010496</t>
+          <t>2012170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>16814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29883</t>
+          <t>29946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41119</t>
+          <t>41218</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739622</t>
+          <t>740809</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>752500</t>
+          <t>752774</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>747291</t>
+          <t>747228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>766894</t>
+          <t>765632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1493678</t>
+          <t>1493579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1515322</t>
+          <t>1515937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>15580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38377</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21011</t>
+          <t>21442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>45497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40576</t>
+          <t>41831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73084</t>
+          <t>72880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>909362</t>
+          <t>912123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931572</t>
+          <t>932159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007720</t>
+          <t>1006404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1030890</t>
+          <t>1030459</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1926556</t>
+          <t>1926760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1959064</t>
+          <t>1957809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50376</t>
+          <t>51408</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85223</t>
+          <t>84834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77457</t>
+          <t>78185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117167</t>
+          <t>119660</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>136242</t>
+          <t>139010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189056</t>
+          <t>190369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3341556</t>
+          <t>3341945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3376403</t>
+          <t>3375371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3436749</t>
+          <t>3434256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3476459</t>
+          <t>3475731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6791638</t>
+          <t>6790325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6844452</t>
+          <t>6841684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2016</t>
+          <t>Población con diagnóstico de asma en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33008</t>
+          <t>32777</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>14717</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33621</t>
+          <t>34217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32560</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58687</t>
+          <t>60696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>641792</t>
+          <t>642023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>660725</t>
+          <t>660973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>639218</t>
+          <t>638622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657440</t>
+          <t>658122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1288952</t>
+          <t>1286943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1315079</t>
+          <t>1314663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>35138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32865</t>
+          <t>33708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60816</t>
+          <t>63929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51648</t>
+          <t>53662</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86392</t>
+          <t>87388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>988035</t>
+          <t>987293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1007802</t>
+          <t>1007675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>982097</t>
+          <t>978984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1010048</t>
+          <t>1009205</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1978952</t>
+          <t>1977956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2013696</t>
+          <t>2011682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21899</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44371</t>
+          <t>43344</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30976</t>
+          <t>30582</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57636</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740404</t>
+          <t>740196</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754348</t>
+          <t>753556</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>740640</t>
+          <t>741667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>763112</t>
+          <t>763691</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1486927</t>
+          <t>1487925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1513587</t>
+          <t>1513981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20928</t>
+          <t>20624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42206</t>
+          <t>43083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56183</t>
+          <t>56930</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>54722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89478</t>
+          <t>88495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>895361</t>
+          <t>894484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916639</t>
+          <t>916943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>987596</t>
+          <t>986849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1013309</t>
+          <t>1013609</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1891868</t>
+          <t>1892851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1926713</t>
+          <t>1926624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68886</t>
+          <t>68851</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104366</t>
+          <t>106386</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117063</t>
+          <t>119238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>165585</t>
+          <t>166235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>197780</t>
+          <t>200126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>257364</t>
+          <t>260204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3289984</t>
+          <t>3287964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3325464</t>
+          <t>3325499</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3378957</t>
+          <t>3378307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3427479</t>
+          <t>3425304</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6681528</t>
+          <t>6678688</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6741112</t>
+          <t>6738766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2023</t>
+          <t>Población con diagnóstico de asma en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>20232</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>45731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>16372</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29716</t>
+          <t>29796</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40390</t>
+          <t>40254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69305</t>
+          <t>70713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>588146</t>
+          <t>589710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>615242</t>
+          <t>615209</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>645135</t>
+          <t>645055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>658607</t>
+          <t>658479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1240987</t>
+          <t>1239579</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1269902</t>
+          <t>1270038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21846</t>
+          <t>21217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68086</t>
+          <t>69487</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29662</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50120</t>
+          <t>48433</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56248</t>
+          <t>54176</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108851</t>
+          <t>108829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1123457</t>
+          <t>1122056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1169697</t>
+          <t>1170326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>907317</t>
+          <t>909004</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>927775</t>
+          <t>928989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2040129</t>
+          <t>2040151</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2092732</t>
+          <t>2094804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40595</t>
+          <t>42308</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52686</t>
+          <t>52620</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36263</t>
+          <t>39298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79379</t>
+          <t>79801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661437</t>
+          <t>659724</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>687744</t>
+          <t>687568</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>879302</t>
+          <t>879368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>914880</t>
+          <t>912380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1554641</t>
+          <t>1554219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1597757</t>
+          <t>1594722</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19252</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40635</t>
+          <t>41702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61208</t>
+          <t>62302</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>311154</t>
+          <t>323035</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88710</t>
+          <t>89403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>405451</t>
+          <t>395814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>886196</t>
+          <t>885129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>907579</t>
+          <t>907577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>779929</t>
+          <t>768048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1029875</t>
+          <t>1028781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1612463</t>
+          <t>1622100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1929204</t>
+          <t>1928511</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94673</t>
+          <t>95309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157388</t>
+          <t>159198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153764</t>
+          <t>152418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>476073</t>
+          <t>508248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>273537</t>
+          <t>273464</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>630304</t>
+          <t>620534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3298459</t>
+          <t>3296649</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3361174</t>
+          <t>3360538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3179286</t>
+          <t>3147111</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3501595</t>
+          <t>3502941</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6480903</t>
+          <t>6490673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6837670</t>
+          <t>6837743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P1409-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1409-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26888</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40689</t>
+          <t>42270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>681458</t>
+          <t>680838</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>695809</t>
+          <t>696226</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>671077</t>
+          <t>670162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>687497</t>
+          <t>687556</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1359830</t>
+          <t>1358249</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1380914</t>
+          <t>1380793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27775</t>
+          <t>28080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>42460</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>34793</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62233</t>
+          <t>61955</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>990172</t>
+          <t>989867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1007731</t>
+          <t>1006643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>985166</t>
+          <t>985331</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1008382</t>
+          <t>1009165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1983505</t>
+          <t>1983783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2012170</t>
+          <t>2010945</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29946</t>
+          <t>29750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18860</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41218</t>
+          <t>42607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740809</t>
+          <t>739850</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>752774</t>
+          <t>752503</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>747228</t>
+          <t>747424</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>765632</t>
+          <t>765908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1493579</t>
+          <t>1492190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1515937</t>
+          <t>1515031</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35616</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45497</t>
+          <t>44369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41831</t>
+          <t>42828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72880</t>
+          <t>74388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912123</t>
+          <t>910797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932159</t>
+          <t>931737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1006404</t>
+          <t>1007532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1030459</t>
+          <t>1029805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1926760</t>
+          <t>1925252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1957809</t>
+          <t>1956812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51408</t>
+          <t>50578</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84834</t>
+          <t>83690</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>77982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119660</t>
+          <t>119290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139010</t>
+          <t>139304</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190369</t>
+          <t>190443</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3341945</t>
+          <t>3343089</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3375371</t>
+          <t>3376201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3434256</t>
+          <t>3434626</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3475731</t>
+          <t>3475934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6790325</t>
+          <t>6790251</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6841684</t>
+          <t>6841390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13827</t>
+          <t>13616</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32777</t>
+          <t>32740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14717</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34217</t>
+          <t>33957</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32976</t>
+          <t>32631</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60696</t>
+          <t>59812</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>642023</t>
+          <t>642060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>660973</t>
+          <t>661184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>638622</t>
+          <t>638882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>658122</t>
+          <t>658053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1286943</t>
+          <t>1287827</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1314663</t>
+          <t>1315008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35138</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33708</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63929</t>
+          <t>61516</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53662</t>
+          <t>54225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87388</t>
+          <t>89550</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>987293</t>
+          <t>989010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1007675</t>
+          <t>1007320</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>978984</t>
+          <t>981397</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1009205</t>
+          <t>1009916</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1977956</t>
+          <t>1975794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2011682</t>
+          <t>2011119</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43344</t>
+          <t>42964</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30582</t>
+          <t>29785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>54572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740196</t>
+          <t>739548</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753556</t>
+          <t>753397</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>741667</t>
+          <t>742047</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>763691</t>
+          <t>764007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1487925</t>
+          <t>1489991</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1513981</t>
+          <t>1514778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20624</t>
+          <t>20634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43083</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>29961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56930</t>
+          <t>56440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54722</t>
+          <t>55140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88495</t>
+          <t>89517</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>894484</t>
+          <t>893912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916943</t>
+          <t>916933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>986849</t>
+          <t>987339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1013609</t>
+          <t>1013818</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1892851</t>
+          <t>1891829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1926624</t>
+          <t>1926206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68851</t>
+          <t>68484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106386</t>
+          <t>106829</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119238</t>
+          <t>119676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166235</t>
+          <t>166461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200126</t>
+          <t>198200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>260204</t>
+          <t>259201</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3287964</t>
+          <t>3287521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3325499</t>
+          <t>3325866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3378307</t>
+          <t>3378081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3425304</t>
+          <t>3424866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6678688</t>
+          <t>6679691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6738766</t>
+          <t>6740692</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30458</t>
+          <t>31405</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45731</t>
+          <t>46609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16372</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29796</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52562</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40254</t>
+          <t>42155</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70713</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>604983</t>
+          <t>659305</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>589710</t>
+          <t>644101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>615209</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>652747</t>
+          <t>709377</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>645055</t>
+          <t>701539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>658479</t>
+          <t>715605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1257730</t>
+          <t>1368682</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1239579</t>
+          <t>1351565</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1270038</t>
+          <t>1380742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674851</t>
+          <t>732187</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674851</t>
+          <t>732187</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674851</t>
+          <t>732187</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310292</t>
+          <t>1422897</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310292</t>
+          <t>1422897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310292</t>
+          <t>1422897</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45128</t>
+          <t>48842</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>32704</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69487</t>
+          <t>69058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37727</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28448</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48433</t>
+          <t>52925</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>82855</t>
+          <t>90319</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54176</t>
+          <t>72067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108829</t>
+          <t>112565</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1146415</t>
+          <t>998677</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1122056</t>
+          <t>978461</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1170326</t>
+          <t>1014815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>919710</t>
+          <t>1028710</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>909004</t>
+          <t>1017262</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>928989</t>
+          <t>1038177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2066125</t>
+          <t>2027387</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2040151</t>
+          <t>2005141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2094804</t>
+          <t>2045639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2148980</t>
+          <t>2117706</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2148980</t>
+          <t>2117706</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2148980</t>
+          <t>2117706</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,102 +5307,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23309</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14464</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42308</t>
+          <t>38381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>43954</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34992</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>57190</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>67454</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>53402</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>85601</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>36744</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19608</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>52620</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>60053</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>39298</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>79801</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -5420,102 +5420,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>678723</t>
+          <t>776727</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>659724</t>
+          <t>761846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>687568</t>
+          <t>786003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>766321</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>753085</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>775283</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>92,94%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>95,68%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1638</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1543048</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1524901</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1557100</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>95,81%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>94,68%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>96,68%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>983</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>895244</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>879368</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>912380</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,06%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,35%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1638</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1573967</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1554219</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1594722</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702032</t>
+          <t>800227</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702032</t>
+          <t>800227</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702032</t>
+          <t>800227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931988</t>
+          <t>810275</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931988</t>
+          <t>810275</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931988</t>
+          <t>810275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634020</t>
+          <t>1610502</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634020</t>
+          <t>1610502</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634020</t>
+          <t>1610502</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28381</t>
+          <t>32134</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41702</t>
+          <t>46863</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>132773</t>
+          <t>69456</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62302</t>
+          <t>55916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>323035</t>
+          <t>83991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>161154</t>
+          <t>101590</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89403</t>
+          <t>84261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>395814</t>
+          <t>122394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>898450</t>
+          <t>957928</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>885129</t>
+          <t>943199</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>907577</t>
+          <t>967223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>958310</t>
+          <t>1047323</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>768048</t>
+          <t>1032788</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1028781</t>
+          <t>1060863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1856760</t>
+          <t>2005251</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1622100</t>
+          <t>1984447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1928511</t>
+          <t>2022580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091083</t>
+          <t>1116779</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091083</t>
+          <t>1116779</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091083</t>
+          <t>1116779</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2017914</t>
+          <t>2106841</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2017914</t>
+          <t>2106841</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2017914</t>
+          <t>2106841</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>127276</t>
+          <t>135881</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95309</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>159198</t>
+          <t>165220</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>229348</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152418</t>
+          <t>158583</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>508248</t>
+          <t>200886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>356624</t>
+          <t>313578</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>273464</t>
+          <t>281706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>620534</t>
+          <t>349650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3328571</t>
+          <t>3392637</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3296649</t>
+          <t>3363298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3360538</t>
+          <t>3417107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3426011</t>
+          <t>3551731</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3147111</t>
+          <t>3528541</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3502941</t>
+          <t>3570844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6754583</t>
+          <t>6944367</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6490673</t>
+          <t>6908295</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6837743</t>
+          <t>6976239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3455847</t>
+          <t>3528518</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3455847</t>
+          <t>3528518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3455847</t>
+          <t>3528518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3655359</t>
+          <t>3729427</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3655359</t>
+          <t>3729427</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3655359</t>
+          <t>3729427</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7111207</t>
+          <t>7257945</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7111207</t>
+          <t>7257945</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7111207</t>
+          <t>7257945</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
